--- a/Luban/Config/Datas/Levels/L14/LevelRules.xlsx
+++ b/Luban/Config/Datas/Levels/L14/LevelRules.xlsx
@@ -703,7 +703,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
